--- a/exports/Explicacoes_Mercado_Bridge_EBITDA.xlsx
+++ b/exports/Explicacoes_Mercado_Bridge_EBITDA.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,25 +417,25 @@
         <v>explicacao</v>
       </c>
       <c r="F1" t="str">
+        <v>linha</v>
+      </c>
+      <c r="G1" t="str">
+        <v>valor_origem</v>
+      </c>
+      <c r="H1" t="str">
+        <v>valor_destino</v>
+      </c>
+      <c r="I1" t="str">
+        <v>variacao</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kt</v>
+      </c>
+      <c r="K1" t="str">
+        <v>impacto_musd</v>
+      </c>
+      <c r="L1" t="str">
         <v>unidade</v>
-      </c>
-      <c r="G1" t="str">
-        <v>linha</v>
-      </c>
-      <c r="H1" t="str">
-        <v>valor_origem</v>
-      </c>
-      <c r="I1" t="str">
-        <v>valor_destino</v>
-      </c>
-      <c r="J1" t="str">
-        <v>variacao</v>
-      </c>
-      <c r="K1" t="str">
-        <v>kt</v>
-      </c>
-      <c r="L1" t="str">
-        <v>impacto_musd</v>
       </c>
     </row>
     <row r="2">
@@ -443,37 +443,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B2" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C2" t="str">
         <v>MRF7</v>
       </c>
       <c r="D2" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E2" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F2" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G2" t="str">
         <v>Iron ore MB 62% (1m lag)</v>
       </c>
+      <c r="G2">
+        <v>96</v>
+      </c>
       <c r="H2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I2">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>0.40025</v>
       </c>
       <c r="K2">
-        <v>4.803</v>
-      </c>
-      <c r="L2">
-        <v>-30</v>
+        <v>-2.5</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="3">
@@ -481,37 +481,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B3" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C3" t="str">
         <v>MRF7</v>
       </c>
       <c r="D3" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E3" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F3" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G3" t="str">
         <v>Iron ore MB 65% (1m lag)</v>
       </c>
+      <c r="G3">
+        <v>109</v>
+      </c>
       <c r="H3">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I3">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>0.47866666666666663</v>
       </c>
       <c r="K3">
-        <v>5.744</v>
-      </c>
-      <c r="L3">
-        <v>-41</v>
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="4">
@@ -519,37 +519,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B4" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C4" t="str">
         <v>MRF7</v>
       </c>
       <c r="D4" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E4" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F4" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G4" t="str">
         <v>Pellet premium</v>
       </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
       <c r="H4">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I4">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>0.45716666666666667</v>
       </c>
       <c r="K4">
-        <v>5.486</v>
-      </c>
-      <c r="L4">
-        <v>-36</v>
+        <v>-3</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="5">
@@ -557,37 +557,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B5" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C5" t="str">
         <v>MRF7</v>
       </c>
       <c r="D5" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E5" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F5" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G5" t="str">
         <v>Rebate (pellet premium)</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
       <c r="H5">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I5">
         <v>-3</v>
       </c>
       <c r="J5">
-        <v>-3</v>
+        <v>0.45716666666666667</v>
       </c>
       <c r="K5">
-        <v>5.486</v>
-      </c>
-      <c r="L5">
-        <v>16</v>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="6">
@@ -595,37 +595,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B6" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C6" t="str">
         <v>MRF7</v>
       </c>
       <c r="D6" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E6" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F6" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G6" t="str">
         <v>Lump premium</v>
       </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
       <c r="H6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="J6">
-        <v>-2</v>
+        <v>0.12816666666666668</v>
       </c>
       <c r="K6">
-        <v>1.538</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
+        <v>0.25</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="7">
@@ -633,37 +633,37 @@
         <v>BUDGET</v>
       </c>
       <c r="B7" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C7" t="str">
         <v>MRF7</v>
       </c>
       <c r="D7" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E7" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F7" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G7" t="str">
         <v>Netback freight</v>
       </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
       <c r="H7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0.8789166666666667</v>
       </c>
       <c r="K7">
-        <v>10.547</v>
-      </c>
-      <c r="L7">
-        <v>41</v>
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="8">
@@ -671,25 +671,25 @@
         <v>BUDGET</v>
       </c>
       <c r="B8" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C8" t="str">
         <v>MRF7</v>
       </c>
       <c r="D8" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E8" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F8" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G8" t="str">
         <v>Forex (contract)</v>
       </c>
-      <c r="L8">
-        <v>-6</v>
+      <c r="K8">
+        <v>-0.5</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
     <row r="9">
@@ -697,37 +697,3117 @@
         <v>BUDGET</v>
       </c>
       <c r="B9" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C9" t="str">
         <v>MRF7</v>
       </c>
       <c r="D9" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E9" t="str">
         <v>Iron Ores</v>
       </c>
       <c r="F9" t="str">
-        <v>Price $/t</v>
-      </c>
-      <c r="G9" t="str">
         <v>Others (Vale contract specification, VIU, open balance)</v>
       </c>
-      <c r="L9">
+      <c r="K9">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B10" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G10">
+        <v>96</v>
+      </c>
+      <c r="H10">
+        <v>103</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10">
+        <v>0.40025</v>
+      </c>
+      <c r="K10">
+        <v>-2.5</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B11" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D11" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G11">
+        <v>109</v>
+      </c>
+      <c r="H11">
+        <v>117</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K11">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B12" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D12" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K12">
+        <v>-3</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B13" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D13" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>-3</v>
+      </c>
+      <c r="I13">
+        <v>-3</v>
+      </c>
+      <c r="J13">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K13">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B14" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C14" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D14" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G14">
+        <v>8</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
         <v>-2</v>
+      </c>
+      <c r="J14">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K14">
+        <v>0.25</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B15" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C15" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D15" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K15">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B16" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D16" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K16">
+        <v>-0.5</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B17" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C17" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D17" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K17">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B18" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C18" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G18">
+        <v>96</v>
+      </c>
+      <c r="H18">
+        <v>103</v>
+      </c>
+      <c r="I18">
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <v>0.40025</v>
+      </c>
+      <c r="K18">
+        <v>-2.5</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B19" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D19" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G19">
+        <v>109</v>
+      </c>
+      <c r="H19">
+        <v>117</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K19">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B20" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C20" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G20">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>37</v>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K20">
+        <v>-3</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B21" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C21" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D21" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>-3</v>
+      </c>
+      <c r="I21">
+        <v>-3</v>
+      </c>
+      <c r="J21">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K21">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B22" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C22" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D22" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>-2</v>
+      </c>
+      <c r="J22">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K22">
+        <v>0.25</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B23" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C23" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D23" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G23">
+        <v>16</v>
+      </c>
+      <c r="H23">
+        <v>20</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K23">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B24" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C24" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D24" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K24">
+        <v>-0.5</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B25" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C25" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K25">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B26" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C26" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D26" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G26">
+        <v>96</v>
+      </c>
+      <c r="H26">
+        <v>103</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <v>0.40025</v>
+      </c>
+      <c r="K26">
+        <v>-2.5</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B27" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D27" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G27">
+        <v>109</v>
+      </c>
+      <c r="H27">
+        <v>117</v>
+      </c>
+      <c r="I27">
+        <v>7</v>
+      </c>
+      <c r="J27">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K27">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B28" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C28" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D28" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G28">
+        <v>30</v>
+      </c>
+      <c r="H28">
+        <v>37</v>
+      </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
+      <c r="J28">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K28">
+        <v>-3</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B29" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C29" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D29" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>-3</v>
+      </c>
+      <c r="I29">
+        <v>-3</v>
+      </c>
+      <c r="J29">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K29">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B30" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C30" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D30" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>-2</v>
+      </c>
+      <c r="J30">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K30">
+        <v>0.25</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B31" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C31" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D31" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G31">
+        <v>16</v>
+      </c>
+      <c r="H31">
+        <v>20</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K31">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B32" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C32" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D32" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K32">
+        <v>-0.5</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B33" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C33" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D33" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K33">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C34" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D34" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G34">
+        <v>96</v>
+      </c>
+      <c r="H34">
+        <v>103</v>
+      </c>
+      <c r="I34">
+        <v>6</v>
+      </c>
+      <c r="J34">
+        <v>0.40025</v>
+      </c>
+      <c r="K34">
+        <v>-2.5</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C35" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D35" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G35">
+        <v>109</v>
+      </c>
+      <c r="H35">
+        <v>117</v>
+      </c>
+      <c r="I35">
+        <v>7</v>
+      </c>
+      <c r="J35">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K35">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B36" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C36" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D36" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G36">
+        <v>30</v>
+      </c>
+      <c r="H36">
+        <v>37</v>
+      </c>
+      <c r="I36">
+        <v>7</v>
+      </c>
+      <c r="J36">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K36">
+        <v>-3</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B37" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C37" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D37" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>-3</v>
+      </c>
+      <c r="I37">
+        <v>-3</v>
+      </c>
+      <c r="J37">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K37">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B38" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C38" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D38" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
+        <v>-2</v>
+      </c>
+      <c r="J38">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K38">
+        <v>0.25</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B39" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C39" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D39" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G39">
+        <v>16</v>
+      </c>
+      <c r="H39">
+        <v>20</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K39">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B40" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C40" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D40" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K40">
+        <v>-0.5</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B41" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C41" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D41" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K41">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B42" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C42" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D42" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G42">
+        <v>96</v>
+      </c>
+      <c r="H42">
+        <v>103</v>
+      </c>
+      <c r="I42">
+        <v>6</v>
+      </c>
+      <c r="J42">
+        <v>0.40025</v>
+      </c>
+      <c r="K42">
+        <v>-2.5</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B43" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C43" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D43" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G43">
+        <v>109</v>
+      </c>
+      <c r="H43">
+        <v>117</v>
+      </c>
+      <c r="I43">
+        <v>7</v>
+      </c>
+      <c r="J43">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K43">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B44" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C44" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D44" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G44">
+        <v>30</v>
+      </c>
+      <c r="H44">
+        <v>37</v>
+      </c>
+      <c r="I44">
+        <v>7</v>
+      </c>
+      <c r="J44">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K44">
+        <v>-3</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B45" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C45" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D45" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>-3</v>
+      </c>
+      <c r="I45">
+        <v>-3</v>
+      </c>
+      <c r="J45">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K45">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B46" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C46" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D46" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G46">
+        <v>8</v>
+      </c>
+      <c r="H46">
+        <v>7</v>
+      </c>
+      <c r="I46">
+        <v>-2</v>
+      </c>
+      <c r="J46">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K46">
+        <v>0.25</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B47" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C47" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D47" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G47">
+        <v>16</v>
+      </c>
+      <c r="H47">
+        <v>20</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K47">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B48" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C48" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D48" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K48">
+        <v>-0.5</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B49" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C49" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D49" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K49">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B50" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C50" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D50" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G50">
+        <v>96</v>
+      </c>
+      <c r="H50">
+        <v>103</v>
+      </c>
+      <c r="I50">
+        <v>6</v>
+      </c>
+      <c r="J50">
+        <v>0.40025</v>
+      </c>
+      <c r="K50">
+        <v>-2.5</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B51" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C51" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D51" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G51">
+        <v>109</v>
+      </c>
+      <c r="H51">
+        <v>117</v>
+      </c>
+      <c r="I51">
+        <v>7</v>
+      </c>
+      <c r="J51">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K51">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B52" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C52" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D52" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G52">
+        <v>30</v>
+      </c>
+      <c r="H52">
+        <v>37</v>
+      </c>
+      <c r="I52">
+        <v>7</v>
+      </c>
+      <c r="J52">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K52">
+        <v>-3</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B53" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C53" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D53" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>-3</v>
+      </c>
+      <c r="I53">
+        <v>-3</v>
+      </c>
+      <c r="J53">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K53">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B54" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C54" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D54" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G54">
+        <v>8</v>
+      </c>
+      <c r="H54">
+        <v>7</v>
+      </c>
+      <c r="I54">
+        <v>-2</v>
+      </c>
+      <c r="J54">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K54">
+        <v>0.25</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B55" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C55" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D55" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G55">
+        <v>16</v>
+      </c>
+      <c r="H55">
+        <v>20</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K55">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B56" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C56" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D56" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K56">
+        <v>-0.5</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B57" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C57" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D57" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K57">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B58" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C58" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D58" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G58">
+        <v>96</v>
+      </c>
+      <c r="H58">
+        <v>103</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
+      </c>
+      <c r="J58">
+        <v>0.40025</v>
+      </c>
+      <c r="K58">
+        <v>-2.5</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B59" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C59" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D59" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G59">
+        <v>109</v>
+      </c>
+      <c r="H59">
+        <v>117</v>
+      </c>
+      <c r="I59">
+        <v>7</v>
+      </c>
+      <c r="J59">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K59">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B60" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C60" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D60" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G60">
+        <v>30</v>
+      </c>
+      <c r="H60">
+        <v>37</v>
+      </c>
+      <c r="I60">
+        <v>7</v>
+      </c>
+      <c r="J60">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K60">
+        <v>-3</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B61" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C61" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D61" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>-3</v>
+      </c>
+      <c r="I61">
+        <v>-3</v>
+      </c>
+      <c r="J61">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K61">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B62" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C62" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D62" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G62">
+        <v>8</v>
+      </c>
+      <c r="H62">
+        <v>7</v>
+      </c>
+      <c r="I62">
+        <v>-2</v>
+      </c>
+      <c r="J62">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K62">
+        <v>0.25</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B63" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C63" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D63" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G63">
+        <v>16</v>
+      </c>
+      <c r="H63">
+        <v>20</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="J63">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K63">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B64" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C64" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D64" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K64">
+        <v>-0.5</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B65" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C65" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D65" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K65">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B66" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C66" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D66" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G66">
+        <v>96</v>
+      </c>
+      <c r="H66">
+        <v>103</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
+      </c>
+      <c r="J66">
+        <v>0.40025</v>
+      </c>
+      <c r="K66">
+        <v>-2.5</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B67" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C67" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D67" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G67">
+        <v>109</v>
+      </c>
+      <c r="H67">
+        <v>117</v>
+      </c>
+      <c r="I67">
+        <v>7</v>
+      </c>
+      <c r="J67">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K67">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B68" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C68" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D68" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="H68">
+        <v>37</v>
+      </c>
+      <c r="I68">
+        <v>7</v>
+      </c>
+      <c r="J68">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K68">
+        <v>-3</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B69" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C69" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D69" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>-3</v>
+      </c>
+      <c r="I69">
+        <v>-3</v>
+      </c>
+      <c r="J69">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K69">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B70" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C70" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D70" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G70">
+        <v>8</v>
+      </c>
+      <c r="H70">
+        <v>7</v>
+      </c>
+      <c r="I70">
+        <v>-2</v>
+      </c>
+      <c r="J70">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K70">
+        <v>0.25</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B71" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C71" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D71" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G71">
+        <v>16</v>
+      </c>
+      <c r="H71">
+        <v>20</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K71">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B72" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C72" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D72" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K72">
+        <v>-0.5</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B73" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C73" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D73" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K73">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B74" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C74" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D74" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G74">
+        <v>96</v>
+      </c>
+      <c r="H74">
+        <v>103</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>0.40025</v>
+      </c>
+      <c r="K74">
+        <v>-2.5</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B75" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C75" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D75" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G75">
+        <v>109</v>
+      </c>
+      <c r="H75">
+        <v>117</v>
+      </c>
+      <c r="I75">
+        <v>7</v>
+      </c>
+      <c r="J75">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K75">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B76" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C76" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D76" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G76">
+        <v>30</v>
+      </c>
+      <c r="H76">
+        <v>37</v>
+      </c>
+      <c r="I76">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K76">
+        <v>-3</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B77" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C77" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D77" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>-3</v>
+      </c>
+      <c r="I77">
+        <v>-3</v>
+      </c>
+      <c r="J77">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K77">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B78" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C78" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D78" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G78">
+        <v>8</v>
+      </c>
+      <c r="H78">
+        <v>7</v>
+      </c>
+      <c r="I78">
+        <v>-2</v>
+      </c>
+      <c r="J78">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K78">
+        <v>0.25</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B79" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C79" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D79" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G79">
+        <v>16</v>
+      </c>
+      <c r="H79">
+        <v>20</v>
+      </c>
+      <c r="I79">
+        <v>4</v>
+      </c>
+      <c r="J79">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K79">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B80" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C80" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D80" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K80">
+        <v>-0.5</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B81" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C81" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D81" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K81">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B82" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C82" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D82" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G82">
+        <v>96</v>
+      </c>
+      <c r="H82">
+        <v>103</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>0.40025</v>
+      </c>
+      <c r="K82">
+        <v>-2.5</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B83" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C83" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D83" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G83">
+        <v>109</v>
+      </c>
+      <c r="H83">
+        <v>117</v>
+      </c>
+      <c r="I83">
+        <v>7</v>
+      </c>
+      <c r="J83">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K83">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B84" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C84" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D84" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G84">
+        <v>30</v>
+      </c>
+      <c r="H84">
+        <v>37</v>
+      </c>
+      <c r="I84">
+        <v>7</v>
+      </c>
+      <c r="J84">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K84">
+        <v>-3</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B85" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C85" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D85" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>-3</v>
+      </c>
+      <c r="I85">
+        <v>-3</v>
+      </c>
+      <c r="J85">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K85">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B86" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C86" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D86" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G86">
+        <v>8</v>
+      </c>
+      <c r="H86">
+        <v>7</v>
+      </c>
+      <c r="I86">
+        <v>-2</v>
+      </c>
+      <c r="J86">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K86">
+        <v>0.25</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B87" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C87" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D87" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G87">
+        <v>16</v>
+      </c>
+      <c r="H87">
+        <v>20</v>
+      </c>
+      <c r="I87">
+        <v>4</v>
+      </c>
+      <c r="J87">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K87">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B88" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C88" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D88" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K88">
+        <v>-0.5</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B89" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C89" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D89" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K89">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B90" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C90" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D90" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Iron ore MB 62% (1m lag)</v>
+      </c>
+      <c r="G90">
+        <v>96</v>
+      </c>
+      <c r="H90">
+        <v>103</v>
+      </c>
+      <c r="I90">
+        <v>6</v>
+      </c>
+      <c r="J90">
+        <v>0.40025</v>
+      </c>
+      <c r="K90">
+        <v>-2.5</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B91" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C91" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D91" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Iron ore MB 65% (1m lag)</v>
+      </c>
+      <c r="G91">
+        <v>109</v>
+      </c>
+      <c r="H91">
+        <v>117</v>
+      </c>
+      <c r="I91">
+        <v>7</v>
+      </c>
+      <c r="J91">
+        <v>0.47866666666666663</v>
+      </c>
+      <c r="K91">
+        <v>-3.4166666666666665</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B92" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C92" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D92" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Pellet premium</v>
+      </c>
+      <c r="G92">
+        <v>30</v>
+      </c>
+      <c r="H92">
+        <v>37</v>
+      </c>
+      <c r="I92">
+        <v>7</v>
+      </c>
+      <c r="J92">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K92">
+        <v>-3</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B93" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C93" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D93" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Rebate (pellet premium)</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>-3</v>
+      </c>
+      <c r="I93">
+        <v>-3</v>
+      </c>
+      <c r="J93">
+        <v>0.45716666666666667</v>
+      </c>
+      <c r="K93">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B94" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C94" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D94" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Lump premium</v>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+      <c r="H94">
+        <v>7</v>
+      </c>
+      <c r="I94">
+        <v>-2</v>
+      </c>
+      <c r="J94">
+        <v>0.12816666666666668</v>
+      </c>
+      <c r="K94">
+        <v>0.25</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B95" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C95" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D95" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Netback freight</v>
+      </c>
+      <c r="G95">
+        <v>16</v>
+      </c>
+      <c r="H95">
+        <v>20</v>
+      </c>
+      <c r="I95">
+        <v>4</v>
+      </c>
+      <c r="J95">
+        <v>0.8789166666666667</v>
+      </c>
+      <c r="K95">
+        <v>3.4166666666666665</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B96" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C96" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D96" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Forex (contract)</v>
+      </c>
+      <c r="K96">
+        <v>-0.5</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Price $/t</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B97" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C97" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D97" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Others (Vale contract specification, VIU, open balance)</v>
+      </c>
+      <c r="K97">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Price $/t</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -754,13 +3834,13 @@
         <v>BUDGET</v>
       </c>
       <c r="B2" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C2" t="str">
         <v>MRF7</v>
       </c>
       <c r="D2" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E2" t="str">
         <v>Iron Ores</v>
@@ -774,13 +3854,13 @@
         <v>BUDGET</v>
       </c>
       <c r="B3" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C3" t="str">
         <v>MRF7</v>
       </c>
       <c r="D3" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E3" t="str">
         <v>Iron Ores</v>
@@ -794,13 +3874,13 @@
         <v>BUDGET</v>
       </c>
       <c r="B4" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="C4" t="str">
         <v>MRF7</v>
       </c>
       <c r="D4" t="str">
-        <v>FY26</v>
+        <v>JAN26</v>
       </c>
       <c r="E4" t="str">
         <v>Iron Ores</v>
@@ -809,9 +3889,669 @@
         <v>Lumps</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B5" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B6" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="C7" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>FEB26</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B9" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B10" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>MAR26</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B11" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D11" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B12" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D12" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B13" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="C13" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D13" t="str">
+        <v>APR26</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B14" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C14" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D14" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C15" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D15" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B16" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="C16" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D16" t="str">
+        <v>MAY26</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B17" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C17" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D17" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B18" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C18" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D18" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B19" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D19" t="str">
+        <v>JUN26</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B20" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C20" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B21" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C21" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D21" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B22" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="C22" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D22" t="str">
+        <v>JUL26</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B23" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C23" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D23" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B24" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C24" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D24" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B25" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="C25" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D25" t="str">
+        <v>AUG26</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C26" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D26" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D27" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="C28" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D28" t="str">
+        <v>SEP26</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B29" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C29" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D29" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B30" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C30" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D30" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B31" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="C31" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D31" t="str">
+        <v>OCT26</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B32" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C32" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D32" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B33" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C33" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D33" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B34" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="C34" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D34" t="str">
+        <v>NOV26</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B35" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C35" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D35" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Fines</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B36" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C36" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D36" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Pellets</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>BUDGET</v>
+      </c>
+      <c r="B37" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="C37" t="str">
+        <v>MRF7</v>
+      </c>
+      <c r="D37" t="str">
+        <v>DEC26</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Iron Ores</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Lumps</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/exports/Explicacoes_Mercado_Bridge_EBITDA.xlsx
+++ b/exports/Explicacoes_Mercado_Bridge_EBITDA.xlsx
@@ -590,7 +590,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B2" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C2" t="str">
         <v>Iron Ores</v>
@@ -610,7 +610,7 @@
         <v>MRF7</v>
       </c>
       <c r="B3" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C3" t="str">
         <v>Iron Ores</v>
@@ -630,7 +630,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B4" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C4" t="str">
         <v>Iron Ores</v>
@@ -650,7 +650,7 @@
         <v>MRF7</v>
       </c>
       <c r="B5" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C5" t="str">
         <v>Iron Ores</v>
@@ -670,7 +670,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B6" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C6" t="str">
         <v>Iron Ores</v>
@@ -690,7 +690,7 @@
         <v>MRF7</v>
       </c>
       <c r="B7" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C7" t="str">
         <v>Iron Ores</v>
@@ -710,7 +710,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B8" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C8" t="str">
         <v>Iron Ores</v>
@@ -730,7 +730,7 @@
         <v>MRF7</v>
       </c>
       <c r="B9" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C9" t="str">
         <v>Iron Ores</v>
@@ -750,7 +750,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B10" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C10" t="str">
         <v>Iron Ores</v>
@@ -770,7 +770,7 @@
         <v>MRF7</v>
       </c>
       <c r="B11" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C11" t="str">
         <v>Iron Ores</v>
@@ -790,7 +790,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B12" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C12" t="str">
         <v>Iron Ores</v>
@@ -810,7 +810,7 @@
         <v>MRF7</v>
       </c>
       <c r="B13" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C13" t="str">
         <v>Iron Ores</v>
@@ -830,7 +830,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B14" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C14" t="str">
         <v>Iron Ores</v>
@@ -850,7 +850,7 @@
         <v>MRF7</v>
       </c>
       <c r="B15" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C15" t="str">
         <v>Iron Ores</v>
@@ -870,7 +870,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B16" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C16" t="str">
         <v>Iron Ores</v>
@@ -890,7 +890,7 @@
         <v>MRF7</v>
       </c>
       <c r="B17" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C17" t="str">
         <v>Iron Ores</v>
@@ -910,7 +910,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B18" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C18" t="str">
         <v>Iron Ores</v>
@@ -930,7 +930,7 @@
         <v>MRF7</v>
       </c>
       <c r="B19" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C19" t="str">
         <v>Iron Ores</v>
@@ -950,7 +950,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B20" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C20" t="str">
         <v>Iron Ores</v>
@@ -970,7 +970,7 @@
         <v>MRF7</v>
       </c>
       <c r="B21" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C21" t="str">
         <v>Iron Ores</v>
@@ -990,7 +990,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B22" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C22" t="str">
         <v>Iron Ores</v>
@@ -1010,7 +1010,7 @@
         <v>MRF7</v>
       </c>
       <c r="B23" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C23" t="str">
         <v>Iron Ores</v>
@@ -1030,7 +1030,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B24" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C24" t="str">
         <v>Iron Ores</v>
@@ -1050,7 +1050,7 @@
         <v>MRF7</v>
       </c>
       <c r="B25" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C25" t="str">
         <v>Iron Ores</v>
@@ -1070,7 +1070,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B26" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C26" t="str">
         <v>Iron Ores</v>
@@ -1090,7 +1090,7 @@
         <v>MRF7</v>
       </c>
       <c r="B27" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C27" t="str">
         <v>Iron Ores</v>
@@ -1110,7 +1110,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B28" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C28" t="str">
         <v>Iron Ores</v>
@@ -1130,7 +1130,7 @@
         <v>MRF7</v>
       </c>
       <c r="B29" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C29" t="str">
         <v>Iron Ores</v>
@@ -1150,7 +1150,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B30" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C30" t="str">
         <v>Iron Ores</v>
@@ -1170,7 +1170,7 @@
         <v>MRF7</v>
       </c>
       <c r="B31" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C31" t="str">
         <v>Iron Ores</v>
@@ -1190,7 +1190,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B32" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C32" t="str">
         <v>Iron Ores</v>
@@ -1210,7 +1210,7 @@
         <v>MRF7</v>
       </c>
       <c r="B33" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C33" t="str">
         <v>Iron Ores</v>
@@ -1230,7 +1230,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B34" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C34" t="str">
         <v>Iron Ores</v>
@@ -1250,7 +1250,7 @@
         <v>MRF7</v>
       </c>
       <c r="B35" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C35" t="str">
         <v>Iron Ores</v>
@@ -1270,7 +1270,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B36" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C36" t="str">
         <v>Iron Ores</v>
@@ -1290,7 +1290,7 @@
         <v>MRF7</v>
       </c>
       <c r="B37" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C37" t="str">
         <v>Iron Ores</v>
@@ -1310,7 +1310,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B38" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C38" t="str">
         <v>Iron Ores</v>
@@ -1330,7 +1330,7 @@
         <v>MRF7</v>
       </c>
       <c r="B39" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C39" t="str">
         <v>Iron Ores</v>
@@ -1350,7 +1350,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B40" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C40" t="str">
         <v>Iron Ores</v>
@@ -1370,7 +1370,7 @@
         <v>MRF7</v>
       </c>
       <c r="B41" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C41" t="str">
         <v>Iron Ores</v>
@@ -1390,7 +1390,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B42" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C42" t="str">
         <v>Iron Ores</v>
@@ -1410,7 +1410,7 @@
         <v>MRF7</v>
       </c>
       <c r="B43" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C43" t="str">
         <v>Iron Ores</v>
@@ -1430,7 +1430,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B44" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C44" t="str">
         <v>Iron Ores</v>
@@ -1450,7 +1450,7 @@
         <v>MRF7</v>
       </c>
       <c r="B45" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C45" t="str">
         <v>Iron Ores</v>
@@ -1470,7 +1470,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B46" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C46" t="str">
         <v>Iron Ores</v>
@@ -1490,7 +1490,7 @@
         <v>MRF7</v>
       </c>
       <c r="B47" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C47" t="str">
         <v>Iron Ores</v>
@@ -1510,7 +1510,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B48" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C48" t="str">
         <v>Iron Ores</v>
@@ -1530,7 +1530,7 @@
         <v>MRF7</v>
       </c>
       <c r="B49" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C49" t="str">
         <v>Iron Ores</v>
@@ -1550,7 +1550,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B50" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C50" t="str">
         <v>Iron Ores</v>
@@ -1570,7 +1570,7 @@
         <v>MRF7</v>
       </c>
       <c r="B51" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C51" t="str">
         <v>Iron Ores</v>
@@ -1590,7 +1590,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B52" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C52" t="str">
         <v>Iron Ores</v>
@@ -1610,7 +1610,7 @@
         <v>MRF7</v>
       </c>
       <c r="B53" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C53" t="str">
         <v>Iron Ores</v>
@@ -1630,7 +1630,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B54" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C54" t="str">
         <v>Iron Ores</v>
@@ -1650,7 +1650,7 @@
         <v>MRF7</v>
       </c>
       <c r="B55" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C55" t="str">
         <v>Iron Ores</v>
@@ -1670,7 +1670,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B56" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C56" t="str">
         <v>Iron Ores</v>
@@ -1690,7 +1690,7 @@
         <v>MRF7</v>
       </c>
       <c r="B57" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C57" t="str">
         <v>Iron Ores</v>
@@ -1710,7 +1710,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B58" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C58" t="str">
         <v>Iron Ores</v>
@@ -1730,7 +1730,7 @@
         <v>MRF7</v>
       </c>
       <c r="B59" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C59" t="str">
         <v>Iron Ores</v>
@@ -1750,7 +1750,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B60" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C60" t="str">
         <v>Iron Ores</v>
@@ -1770,7 +1770,7 @@
         <v>MRF7</v>
       </c>
       <c r="B61" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C61" t="str">
         <v>Iron Ores</v>
@@ -1790,7 +1790,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B62" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C62" t="str">
         <v>Iron Ores</v>
@@ -1810,7 +1810,7 @@
         <v>MRF7</v>
       </c>
       <c r="B63" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C63" t="str">
         <v>Iron Ores</v>
@@ -1830,7 +1830,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B64" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C64" t="str">
         <v>Iron Ores</v>
@@ -1850,7 +1850,7 @@
         <v>MRF7</v>
       </c>
       <c r="B65" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C65" t="str">
         <v>Iron Ores</v>
@@ -1870,7 +1870,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B66" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C66" t="str">
         <v>Iron Ores</v>
@@ -1890,7 +1890,7 @@
         <v>MRF7</v>
       </c>
       <c r="B67" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C67" t="str">
         <v>Iron Ores</v>
@@ -1910,7 +1910,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B68" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C68" t="str">
         <v>Iron Ores</v>
@@ -1930,7 +1930,7 @@
         <v>MRF7</v>
       </c>
       <c r="B69" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C69" t="str">
         <v>Iron Ores</v>
@@ -1950,7 +1950,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B70" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C70" t="str">
         <v>Iron Ores</v>
@@ -1970,7 +1970,7 @@
         <v>MRF7</v>
       </c>
       <c r="B71" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C71" t="str">
         <v>Iron Ores</v>
@@ -1990,7 +1990,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B72" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C72" t="str">
         <v>Iron Ores</v>
@@ -2010,7 +2010,7 @@
         <v>MRF7</v>
       </c>
       <c r="B73" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C73" t="str">
         <v>Iron Ores</v>
@@ -2030,7 +2030,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B74" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C74" t="str">
         <v>Iron Ores</v>
@@ -2050,7 +2050,7 @@
         <v>MRF7</v>
       </c>
       <c r="B75" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C75" t="str">
         <v>Iron Ores</v>
@@ -2070,7 +2070,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B76" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C76" t="str">
         <v>Iron Ores</v>
@@ -2090,7 +2090,7 @@
         <v>MRF7</v>
       </c>
       <c r="B77" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C77" t="str">
         <v>Iron Ores</v>
@@ -2110,7 +2110,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B78" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C78" t="str">
         <v>Iron Ores</v>
@@ -2130,7 +2130,7 @@
         <v>MRF7</v>
       </c>
       <c r="B79" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C79" t="str">
         <v>Iron Ores</v>
@@ -2150,7 +2150,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B80" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C80" t="str">
         <v>Iron Ores</v>
@@ -2170,7 +2170,7 @@
         <v>MRF7</v>
       </c>
       <c r="B81" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C81" t="str">
         <v>Iron Ores</v>
@@ -2190,7 +2190,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B82" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C82" t="str">
         <v>Iron Ores</v>
@@ -2210,7 +2210,7 @@
         <v>MRF7</v>
       </c>
       <c r="B83" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C83" t="str">
         <v>Iron Ores</v>
@@ -2230,7 +2230,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B84" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C84" t="str">
         <v>Iron Ores</v>
@@ -2250,7 +2250,7 @@
         <v>MRF7</v>
       </c>
       <c r="B85" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C85" t="str">
         <v>Iron Ores</v>
@@ -2270,7 +2270,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B86" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C86" t="str">
         <v>Iron Ores</v>
@@ -2290,7 +2290,7 @@
         <v>MRF7</v>
       </c>
       <c r="B87" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C87" t="str">
         <v>Iron Ores</v>
@@ -2310,7 +2310,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B88" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C88" t="str">
         <v>Iron Ores</v>
@@ -2330,7 +2330,7 @@
         <v>MRF7</v>
       </c>
       <c r="B89" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C89" t="str">
         <v>Iron Ores</v>
@@ -2350,7 +2350,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B90" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C90" t="str">
         <v>Iron Ores</v>
@@ -2370,7 +2370,7 @@
         <v>MRF7</v>
       </c>
       <c r="B91" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C91" t="str">
         <v>Iron Ores</v>
@@ -2390,7 +2390,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B92" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C92" t="str">
         <v>Iron Ores</v>
@@ -2410,7 +2410,7 @@
         <v>MRF7</v>
       </c>
       <c r="B93" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C93" t="str">
         <v>Iron Ores</v>
@@ -2430,7 +2430,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B94" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C94" t="str">
         <v>Iron Ores</v>
@@ -2450,7 +2450,7 @@
         <v>MRF7</v>
       </c>
       <c r="B95" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C95" t="str">
         <v>Iron Ores</v>
@@ -2470,7 +2470,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B96" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C96" t="str">
         <v>Iron Ores</v>
@@ -2490,7 +2490,7 @@
         <v>MRF7</v>
       </c>
       <c r="B97" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C97" t="str">
         <v>Iron Ores</v>
@@ -2510,7 +2510,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B98" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C98" t="str">
         <v>Iron Ores</v>
@@ -2530,7 +2530,7 @@
         <v>MRF7</v>
       </c>
       <c r="B99" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C99" t="str">
         <v>Iron Ores</v>
@@ -2550,7 +2550,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B100" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C100" t="str">
         <v>Iron Ores</v>
@@ -2570,7 +2570,7 @@
         <v>MRF7</v>
       </c>
       <c r="B101" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C101" t="str">
         <v>Iron Ores</v>
@@ -2590,7 +2590,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B102" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C102" t="str">
         <v>Iron Ores</v>
@@ -2610,7 +2610,7 @@
         <v>MRF7</v>
       </c>
       <c r="B103" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C103" t="str">
         <v>Iron Ores</v>
@@ -2630,7 +2630,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B104" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C104" t="str">
         <v>Iron Ores</v>
@@ -2650,7 +2650,7 @@
         <v>MRF7</v>
       </c>
       <c r="B105" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C105" t="str">
         <v>Iron Ores</v>
@@ -2670,7 +2670,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B106" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C106" t="str">
         <v>Iron Ores</v>
@@ -2690,7 +2690,7 @@
         <v>MRF7</v>
       </c>
       <c r="B107" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C107" t="str">
         <v>Iron Ores</v>
@@ -2710,7 +2710,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B108" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C108" t="str">
         <v>Iron Ores</v>
@@ -2730,7 +2730,7 @@
         <v>MRF7</v>
       </c>
       <c r="B109" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C109" t="str">
         <v>Iron Ores</v>
@@ -2750,7 +2750,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B110" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C110" t="str">
         <v>Iron Ores</v>
@@ -2770,7 +2770,7 @@
         <v>MRF7</v>
       </c>
       <c r="B111" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C111" t="str">
         <v>Iron Ores</v>
@@ -2790,7 +2790,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B112" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C112" t="str">
         <v>Iron Ores</v>
@@ -2810,7 +2810,7 @@
         <v>MRF7</v>
       </c>
       <c r="B113" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C113" t="str">
         <v>Iron Ores</v>
@@ -2830,7 +2830,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B114" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C114" t="str">
         <v>Iron Ores</v>
@@ -2850,7 +2850,7 @@
         <v>MRF7</v>
       </c>
       <c r="B115" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C115" t="str">
         <v>Iron Ores</v>
@@ -2870,7 +2870,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B116" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C116" t="str">
         <v>Iron Ores</v>
@@ -2890,7 +2890,7 @@
         <v>MRF7</v>
       </c>
       <c r="B117" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C117" t="str">
         <v>Iron Ores</v>
@@ -2910,7 +2910,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B118" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C118" t="str">
         <v>Iron Ores</v>
@@ -2930,7 +2930,7 @@
         <v>MRF7</v>
       </c>
       <c r="B119" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C119" t="str">
         <v>Iron Ores</v>
@@ -2950,7 +2950,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B120" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C120" t="str">
         <v>Iron Ores</v>
@@ -2970,7 +2970,7 @@
         <v>MRF7</v>
       </c>
       <c r="B121" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C121" t="str">
         <v>Iron Ores</v>
@@ -2990,7 +2990,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B122" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C122" t="str">
         <v>Iron Ores</v>
@@ -3010,7 +3010,7 @@
         <v>MRF7</v>
       </c>
       <c r="B123" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C123" t="str">
         <v>Iron Ores</v>
@@ -3030,7 +3030,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B124" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C124" t="str">
         <v>Iron Ores</v>
@@ -3050,7 +3050,7 @@
         <v>MRF7</v>
       </c>
       <c r="B125" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C125" t="str">
         <v>Iron Ores</v>
@@ -3070,7 +3070,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B126" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C126" t="str">
         <v>Iron Ores</v>
@@ -3090,7 +3090,7 @@
         <v>MRF7</v>
       </c>
       <c r="B127" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C127" t="str">
         <v>Iron Ores</v>
@@ -3110,7 +3110,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B128" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C128" t="str">
         <v>Iron Ores</v>
@@ -3130,7 +3130,7 @@
         <v>MRF7</v>
       </c>
       <c r="B129" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C129" t="str">
         <v>Iron Ores</v>
@@ -3150,7 +3150,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B130" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C130" t="str">
         <v>Iron Ores</v>
@@ -3170,7 +3170,7 @@
         <v>MRF7</v>
       </c>
       <c r="B131" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C131" t="str">
         <v>Iron Ores</v>
@@ -3190,7 +3190,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B132" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C132" t="str">
         <v>Iron Ores</v>
@@ -3210,7 +3210,7 @@
         <v>MRF7</v>
       </c>
       <c r="B133" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C133" t="str">
         <v>Iron Ores</v>
@@ -3230,7 +3230,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B134" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C134" t="str">
         <v>Iron Ores</v>
@@ -3250,7 +3250,7 @@
         <v>MRF7</v>
       </c>
       <c r="B135" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C135" t="str">
         <v>Iron Ores</v>
@@ -3270,7 +3270,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B136" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C136" t="str">
         <v>Iron Ores</v>
@@ -3290,7 +3290,7 @@
         <v>MRF7</v>
       </c>
       <c r="B137" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C137" t="str">
         <v>Iron Ores</v>
@@ -3310,7 +3310,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B138" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C138" t="str">
         <v>Iron Ores</v>
@@ -3330,7 +3330,7 @@
         <v>MRF7</v>
       </c>
       <c r="B139" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C139" t="str">
         <v>Iron Ores</v>
@@ -3350,7 +3350,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B140" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C140" t="str">
         <v>Iron Ores</v>
@@ -3370,7 +3370,7 @@
         <v>MRF7</v>
       </c>
       <c r="B141" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C141" t="str">
         <v>Iron Ores</v>
@@ -3390,7 +3390,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B142" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C142" t="str">
         <v>Iron Ores</v>
@@ -3410,7 +3410,7 @@
         <v>MRF7</v>
       </c>
       <c r="B143" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C143" t="str">
         <v>Iron Ores</v>
@@ -3430,7 +3430,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B144" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C144" t="str">
         <v>Iron Ores</v>
@@ -3450,7 +3450,7 @@
         <v>MRF7</v>
       </c>
       <c r="B145" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C145" t="str">
         <v>Iron Ores</v>
@@ -3470,7 +3470,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B146" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C146" t="str">
         <v>Iron Ores</v>
@@ -3487,7 +3487,7 @@
         <v>MRF7</v>
       </c>
       <c r="B147" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C147" t="str">
         <v>Iron Ores</v>
@@ -3504,7 +3504,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B148" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C148" t="str">
         <v>Iron Ores</v>
@@ -3521,7 +3521,7 @@
         <v>MRF7</v>
       </c>
       <c r="B149" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C149" t="str">
         <v>Iron Ores</v>
@@ -3538,7 +3538,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B150" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C150" t="str">
         <v>Iron Ores</v>
@@ -3555,7 +3555,7 @@
         <v>MRF7</v>
       </c>
       <c r="B151" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C151" t="str">
         <v>Iron Ores</v>
@@ -3572,7 +3572,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B152" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C152" t="str">
         <v>Iron Ores</v>
@@ -3589,7 +3589,7 @@
         <v>MRF7</v>
       </c>
       <c r="B153" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C153" t="str">
         <v>Iron Ores</v>
@@ -3606,7 +3606,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B154" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C154" t="str">
         <v>Iron Ores</v>
@@ -3623,7 +3623,7 @@
         <v>MRF7</v>
       </c>
       <c r="B155" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C155" t="str">
         <v>Iron Ores</v>
@@ -3640,7 +3640,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B156" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C156" t="str">
         <v>Iron Ores</v>
@@ -3657,7 +3657,7 @@
         <v>MRF7</v>
       </c>
       <c r="B157" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C157" t="str">
         <v>Iron Ores</v>
@@ -3674,7 +3674,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B158" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C158" t="str">
         <v>Iron Ores</v>
@@ -3691,7 +3691,7 @@
         <v>MRF7</v>
       </c>
       <c r="B159" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C159" t="str">
         <v>Iron Ores</v>
@@ -3708,7 +3708,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B160" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C160" t="str">
         <v>Iron Ores</v>
@@ -3725,7 +3725,7 @@
         <v>MRF7</v>
       </c>
       <c r="B161" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C161" t="str">
         <v>Iron Ores</v>
@@ -3742,7 +3742,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B162" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C162" t="str">
         <v>Iron Ores</v>
@@ -3759,7 +3759,7 @@
         <v>MRF7</v>
       </c>
       <c r="B163" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C163" t="str">
         <v>Iron Ores</v>
@@ -3776,7 +3776,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B164" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C164" t="str">
         <v>Iron Ores</v>
@@ -3793,7 +3793,7 @@
         <v>MRF7</v>
       </c>
       <c r="B165" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C165" t="str">
         <v>Iron Ores</v>
@@ -3810,7 +3810,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B166" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C166" t="str">
         <v>Iron Ores</v>
@@ -3827,7 +3827,7 @@
         <v>MRF7</v>
       </c>
       <c r="B167" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C167" t="str">
         <v>Iron Ores</v>
@@ -3844,7 +3844,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B168" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C168" t="str">
         <v>Iron Ores</v>
@@ -3861,7 +3861,7 @@
         <v>MRF7</v>
       </c>
       <c r="B169" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C169" t="str">
         <v>Iron Ores</v>
@@ -3878,7 +3878,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B170" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C170" t="str">
         <v>Iron Ores</v>
@@ -3895,7 +3895,7 @@
         <v>MRF7</v>
       </c>
       <c r="B171" t="str">
-        <v>JAN26</v>
+        <v>202601</v>
       </c>
       <c r="C171" t="str">
         <v>Iron Ores</v>
@@ -3912,7 +3912,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B172" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C172" t="str">
         <v>Iron Ores</v>
@@ -3929,7 +3929,7 @@
         <v>MRF7</v>
       </c>
       <c r="B173" t="str">
-        <v>FEB26</v>
+        <v>202602</v>
       </c>
       <c r="C173" t="str">
         <v>Iron Ores</v>
@@ -3946,7 +3946,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B174" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C174" t="str">
         <v>Iron Ores</v>
@@ -3963,7 +3963,7 @@
         <v>MRF7</v>
       </c>
       <c r="B175" t="str">
-        <v>MAR26</v>
+        <v>202603</v>
       </c>
       <c r="C175" t="str">
         <v>Iron Ores</v>
@@ -3980,7 +3980,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B176" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C176" t="str">
         <v>Iron Ores</v>
@@ -3997,7 +3997,7 @@
         <v>MRF7</v>
       </c>
       <c r="B177" t="str">
-        <v>APR26</v>
+        <v>202604</v>
       </c>
       <c r="C177" t="str">
         <v>Iron Ores</v>
@@ -4014,7 +4014,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B178" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C178" t="str">
         <v>Iron Ores</v>
@@ -4031,7 +4031,7 @@
         <v>MRF7</v>
       </c>
       <c r="B179" t="str">
-        <v>MAY26</v>
+        <v>202605</v>
       </c>
       <c r="C179" t="str">
         <v>Iron Ores</v>
@@ -4048,7 +4048,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B180" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C180" t="str">
         <v>Iron Ores</v>
@@ -4065,7 +4065,7 @@
         <v>MRF7</v>
       </c>
       <c r="B181" t="str">
-        <v>JUN26</v>
+        <v>202606</v>
       </c>
       <c r="C181" t="str">
         <v>Iron Ores</v>
@@ -4082,7 +4082,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B182" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C182" t="str">
         <v>Iron Ores</v>
@@ -4099,7 +4099,7 @@
         <v>MRF7</v>
       </c>
       <c r="B183" t="str">
-        <v>JUL26</v>
+        <v>202607</v>
       </c>
       <c r="C183" t="str">
         <v>Iron Ores</v>
@@ -4116,7 +4116,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B184" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C184" t="str">
         <v>Iron Ores</v>
@@ -4133,7 +4133,7 @@
         <v>MRF7</v>
       </c>
       <c r="B185" t="str">
-        <v>AUG26</v>
+        <v>202608</v>
       </c>
       <c r="C185" t="str">
         <v>Iron Ores</v>
@@ -4150,7 +4150,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B186" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C186" t="str">
         <v>Iron Ores</v>
@@ -4167,7 +4167,7 @@
         <v>MRF7</v>
       </c>
       <c r="B187" t="str">
-        <v>SEP26</v>
+        <v>202609</v>
       </c>
       <c r="C187" t="str">
         <v>Iron Ores</v>
@@ -4184,7 +4184,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B188" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C188" t="str">
         <v>Iron Ores</v>
@@ -4201,7 +4201,7 @@
         <v>MRF7</v>
       </c>
       <c r="B189" t="str">
-        <v>OCT26</v>
+        <v>202610</v>
       </c>
       <c r="C189" t="str">
         <v>Iron Ores</v>
@@ -4218,7 +4218,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B190" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C190" t="str">
         <v>Iron Ores</v>
@@ -4235,7 +4235,7 @@
         <v>MRF7</v>
       </c>
       <c r="B191" t="str">
-        <v>NOV26</v>
+        <v>202611</v>
       </c>
       <c r="C191" t="str">
         <v>Iron Ores</v>
@@ -4252,7 +4252,7 @@
         <v>BUDGET</v>
       </c>
       <c r="B192" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C192" t="str">
         <v>Iron Ores</v>
@@ -4269,7 +4269,7 @@
         <v>MRF7</v>
       </c>
       <c r="B193" t="str">
-        <v>DEC26</v>
+        <v>202612</v>
       </c>
       <c r="C193" t="str">
         <v>Iron Ores</v>
